--- a/backend/src/templates/template-sinh-vien.xlsx
+++ b/backend/src/templates/template-sinh-vien.xlsx
@@ -4,58 +4,49 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
-    <sheet sheetId="1" name="Danh sách sinh viên" state="visible" r:id="rId4"/>
+    <sheet sheetId="1" name="Sinh viên" state="visible" r:id="rId4"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="29">
-  <si>
-    <t>Mã sinh viên</t>
-  </si>
-  <si>
-    <t>Họ tên</t>
-  </si>
-  <si>
-    <t>Email</t>
-  </si>
-  <si>
-    <t>Mật khẩu</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
+  <si>
+    <t>Mã SV</t>
+  </si>
+  <si>
+    <t>Họ và tên</t>
+  </si>
+  <si>
+    <t>Số điện thoại</t>
   </si>
   <si>
     <t>Lớp</t>
   </si>
   <si>
-    <t>Khoa</t>
-  </si>
-  <si>
-    <t>Ngành</t>
-  </si>
-  <si>
-    <t>Khóa học</t>
-  </si>
-  <si>
     <t>Ngày sinh</t>
   </si>
   <si>
-    <t>Giới tính</t>
-  </si>
-  <si>
-    <t>Địa chỉ</t>
-  </si>
-  <si>
-    <t>Số điện thoại</t>
-  </si>
-  <si>
-    <t>Email cá nhân</t>
-  </si>
-  <si>
-    <t>GPA</t>
-  </si>
-  <si>
-    <t>Tình trạng học tập</t>
+    <t>TT Học</t>
+  </si>
+  <si>
+    <t>TBCHT H10</t>
+  </si>
+  <si>
+    <t>Xếp loại</t>
+  </si>
+  <si>
+    <t>Số.TC TLũy</t>
+  </si>
+  <si>
+    <t>Số.TC HT</t>
+  </si>
+  <si>
+    <t>Năm thứ</t>
+  </si>
+  <si>
+    <t>HP Nợ</t>
   </si>
   <si>
     <t>SV001</t>
@@ -64,40 +55,34 @@
     <t>Nguyễn Văn A</t>
   </si>
   <si>
-    <t>sv001@dainam.edu.vn</t>
-  </si>
-  <si>
-    <t>123456</t>
+    <t>0123456789</t>
   </si>
   <si>
     <t>CNTT01</t>
   </si>
   <si>
-    <t>Công nghệ thông tin</t>
-  </si>
-  <si>
-    <t>K18</t>
-  </si>
-  <si>
-    <t>2000-01-15</t>
-  </si>
-  <si>
-    <t>Nam</t>
-  </si>
-  <si>
-    <t>Hà Nội</t>
-  </si>
-  <si>
-    <t>0123456789</t>
-  </si>
-  <si>
-    <t>nguyenvana@gmail.com</t>
-  </si>
-  <si>
-    <t>3.5</t>
+    <t>26/06/2004</t>
   </si>
   <si>
     <t>Đang học</t>
+  </si>
+  <si>
+    <t>3.50</t>
+  </si>
+  <si>
+    <t>Giỏi</t>
+  </si>
+  <si>
+    <t>110</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>0</t>
   </si>
 </sst>
 </file>
@@ -114,6 +99,7 @@
     </font>
     <font>
       <b/>
+      <color rgb="FFFFFFFF"/>
     </font>
   </fonts>
   <fills count="3">
@@ -125,11 +111,11 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE6F3FF"/>
+        <fgColor rgb="FF4472C4"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -137,13 +123,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -483,101 +477,86 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O2"/>
+  <dimension ref="A1:L2"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="12" width="16" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="B2" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="C2" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="D2" t="s">
         <v>15</v>
       </c>
-      <c r="B2" t="s">
+      <c r="E2" t="s">
         <v>16</v>
       </c>
-      <c r="C2" t="s">
+      <c r="F2" t="s">
         <v>17</v>
       </c>
-      <c r="D2" t="s">
+      <c r="G2" t="s">
         <v>18</v>
       </c>
-      <c r="E2" t="s">
+      <c r="H2" t="s">
         <v>19</v>
       </c>
-      <c r="F2" t="s">
+      <c r="I2" t="s">
         <v>20</v>
       </c>
-      <c r="G2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H2" t="s">
+      <c r="J2" t="s">
         <v>21</v>
       </c>
-      <c r="I2" t="s">
+      <c r="K2" t="s">
         <v>22</v>
       </c>
-      <c r="J2" t="s">
+      <c r="L2" t="s">
         <v>23</v>
-      </c>
-      <c r="K2" t="s">
-        <v>24</v>
-      </c>
-      <c r="L2" t="s">
-        <v>25</v>
-      </c>
-      <c r="M2" t="s">
-        <v>26</v>
-      </c>
-      <c r="N2" t="s">
-        <v>27</v>
-      </c>
-      <c r="O2" t="s">
-        <v>28</v>
       </c>
     </row>
   </sheetData>
